--- a/documentation/stack spreadsheet.xlsx
+++ b/documentation/stack spreadsheet.xlsx
@@ -20,7 +20,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+  <si>
+    <t xml:space="preserve">Requirement ID</t>
+  </si>
   <si>
     <t xml:space="preserve">Item</t>
   </si>
@@ -34,6 +37,9 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
+    <t xml:space="preserve">Sprint No.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Items:</t>
   </si>
   <si>
@@ -52,16 +58,22 @@
     <t xml:space="preserve">Detect mouse movements to indicate swapping tiles</t>
   </si>
   <si>
+    <t xml:space="preserve">Sprints:</t>
+  </si>
+  <si>
     <t xml:space="preserve">Swapping Tiles</t>
   </si>
   <si>
     <t xml:space="preserve">Functionality to move/swap tiles</t>
   </si>
   <si>
+    <t xml:space="preserve">Story Points/Sprint:</t>
+  </si>
+  <si>
     <t xml:space="preserve">Detecting Matches</t>
   </si>
   <si>
-    <t xml:space="preserve">Detecting matches in a general sense</t>
+    <t xml:space="preserve">Detecting matches in a general sense (detecting every tile involved in tile in the match)</t>
   </si>
   <si>
     <t xml:space="preserve">Tile Clearing Mechanic</t>
@@ -91,7 +103,7 @@
     <t xml:space="preserve">Powerup creation</t>
   </si>
   <si>
-    <t xml:space="preserve">Create powerup after a special match</t>
+    <t xml:space="preserve">Create powerup after a special match (i.e. the powerup tile itself on the board)</t>
   </si>
   <si>
     <t xml:space="preserve">Powerups</t>
@@ -197,7 +209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -220,13 +232,26 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2A6099"/>
+        <bgColor rgb="FF666699"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -263,8 +288,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -277,7 +306,15 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF2A6099"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -293,7 +330,75 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="FF000000"/>
+      <rgbColor rgb="FFFFFFFF"/>
+      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FF00FF00"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008000"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FF808000"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FF808080"/>
+      <rgbColor rgb="FF9999FF"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FFFFFFCC"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FF660066"/>
+      <rgbColor rgb="FFFF8080"/>
+      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FFCCCCFF"/>
+      <rgbColor rgb="FF000080"/>
+      <rgbColor rgb="FFFF00FF"/>
+      <rgbColor rgb="FFFFFF00"/>
+      <rgbColor rgb="FF00FFFF"/>
+      <rgbColor rgb="FF800080"/>
+      <rgbColor rgb="FF800000"/>
+      <rgbColor rgb="FF008080"/>
+      <rgbColor rgb="FF0000FF"/>
+      <rgbColor rgb="FF00CCFF"/>
+      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFCCFFCC"/>
+      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FF99CCFF"/>
+      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFCC99FF"/>
+      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FF3366FF"/>
+      <rgbColor rgb="FF33CCCC"/>
+      <rgbColor rgb="FF99CC00"/>
+      <rgbColor rgb="FFFFCC00"/>
+      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFFF6600"/>
+      <rgbColor rgb="FF666699"/>
+      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FF003366"/>
+      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF003300"/>
+      <rgbColor rgb="FF333300"/>
+      <rgbColor rgb="FF993300"/>
+      <rgbColor rgb="FF993366"/>
+      <rgbColor rgb="FF333399"/>
+      <rgbColor rgb="FF333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -474,316 +579,487 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="0" width="11.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="83.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="16.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="11.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="86.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.98"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+    <row r="1" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="0" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="0" t="s">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="0" t="n">
-        <f aca="false">COUNTA(A2:A10000)</f>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="1" t="n">
+        <f aca="false">COUNTA(B2:B10000)</f>
         <v>25</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" s="0" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="s">
+      <c r="B2" s="0" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="H2" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="0" t="n">
+        <f aca="false">SUM(D:D)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="0" t="s">
+        <v>11</v>
+      </c>
+      <c r="H3" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="I3" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="F2" s="0" t="s">
+    </row>
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" s="0" t="n">
+        <f aca="false">I2/I3</f>
+        <v>12.6666666666667</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="0" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D5" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="D7" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="n">
         <v>7</v>
       </c>
-      <c r="G2" s="0" t="n">
-        <f aca="false">SUM(C:C)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="s">
+      <c r="B8" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="0" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B3" s="0" t="n">
+      <c r="B9" s="0" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="0" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="0" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="0" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="0" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="0" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="0" t="s">
+      <c r="E12" s="0" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="0" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="0" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="0" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="0" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="0" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D14" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="0" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="0" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="0" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D15" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="0" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="0" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="0" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D16" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="0" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D17" s="0" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="0" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="D18" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="0" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="0" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="0" t="n">
+        <v>6</v>
+      </c>
+      <c r="D19" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="0" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="0" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D20" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="0" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="0" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="D21" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="0" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="0" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D22" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="0" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="0" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="0" t="n">
+        <v>8</v>
+      </c>
+      <c r="D23" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="0" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="0" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="0" t="n">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="D4" s="0" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="B6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="0" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="s">
-        <v>16</v>
-      </c>
-      <c r="B7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="0" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>18</v>
-      </c>
-      <c r="B8" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="s">
-        <v>20</v>
-      </c>
-      <c r="B9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="0" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="s">
-        <v>22</v>
-      </c>
-      <c r="B10" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="s">
+      <c r="D24" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="0" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
         <v>24</v>
       </c>
-      <c r="B11" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="0" t="s">
+      <c r="B25" s="0" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="0" t="n">
+        <v>9</v>
+      </c>
+      <c r="D25" s="0" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="0" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
         <v>25</v>
       </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="0" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="B13" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="B14" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="0" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="0" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="B16" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="B19" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="B20" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D20" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D21" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="B23" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="0" t="n">
+      <c r="B26" s="0" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="D24" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D25" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="B26" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D26" s="0" t="s">
-        <v>55</v>
+      <c r="D26" s="0" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="0" t="s">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/stack spreadsheet.xlsx
+++ b/documentation/stack spreadsheet.xlsx
@@ -25,16 +25,16 @@
     <t xml:space="preserve">Requirement ID</t>
   </si>
   <si>
-    <t xml:space="preserve">Item</t>
+    <t xml:space="preserve">Item Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Story Points</t>
   </si>
   <si>
     <t xml:space="preserve">Priority</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Story Points</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint No.</t>
@@ -288,12 +288,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -306,39 +314,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF2A6099"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -579,487 +554,489 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="16.54"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="32.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="11.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="86.65"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.84"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="19.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="86.65"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.84"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.98"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" s="2" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="1" t="s">
+      <c r="F1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="I1" s="2" t="n">
         <f aca="false">COUNTA(B2:B10000)</f>
         <v>25</v>
       </c>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="0" t="s">
+      <c r="B2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D2" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="0" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="0" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="0" t="n">
+      <c r="I2" s="1" t="n">
         <f aca="false">SUM(D:D)</f>
         <v>76</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="0" t="s">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D3" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="0" t="s">
-        <v>11</v>
-      </c>
-      <c r="H3" s="0" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="0" t="n">
+      <c r="I3" s="1" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="0" t="s">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="D4" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="0" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="0" t="s">
+      <c r="H4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="0" t="n">
+      <c r="I4" s="1" t="n">
         <f aca="false">I2/I3</f>
         <v>12.6666666666667</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="0" t="n">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="0" t="s">
+      <c r="B5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E5" s="0" t="s">
+      <c r="C5" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="D5" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="0" t="s">
+      <c r="A6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D6" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="0" t="s">
+      <c r="C6" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="D6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="0" t="n">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="0" t="s">
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="0" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
+      <c r="D7" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>2</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="n">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="0" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="0" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
+      <c r="D8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="0" t="n">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="0" t="s">
+      <c r="B9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="0" t="s">
+      <c r="C9" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="D9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="0" t="n">
+      <c r="A10" s="1" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D17" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D19" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" s="1" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="1" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="0" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D10" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="0" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="0" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="0" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="0" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="0" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="0" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="0" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="0" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="0" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="0" t="n">
-        <v>13</v>
-      </c>
-      <c r="B14" s="0" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="0" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="0" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="0" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D15" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E15" s="0" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="0" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="0" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D16" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="0" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="0" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D17" s="0" t="n">
-        <v>2</v>
-      </c>
-      <c r="E17" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="0" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" s="0" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="D18" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="E18" s="0" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="0" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" s="0" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="0" t="n">
-        <v>6</v>
-      </c>
-      <c r="D19" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E19" s="0" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="0" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" s="0" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D20" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" s="0" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="0" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" s="0" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="0" t="n">
-        <v>7</v>
-      </c>
-      <c r="D21" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="0" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="0" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" s="0" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D22" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E22" s="0" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="0" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" s="0" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="0" t="n">
-        <v>8</v>
-      </c>
-      <c r="D23" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E23" s="0" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="0" t="n">
+    </row>
+    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B24" s="0" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="0" t="n">
+      <c r="B25" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D25" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="D24" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E24" s="0" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="0" t="n">
+    </row>
+    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B25" s="0" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="0" t="n">
+      <c r="B26" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D26" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" s="1" t="n">
         <v>9</v>
-      </c>
-      <c r="D25" s="0" t="n">
-        <v>3</v>
-      </c>
-      <c r="E25" s="0" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="0" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="0" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="0" t="n">
-        <v>9</v>
-      </c>
-      <c r="D26" s="0" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="0" t="s">
-        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/stack spreadsheet.xlsx
+++ b/documentation/stack spreadsheet.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="7"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="Calc"/>
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Requirements Stack" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Requirements Stack" sheetId="1" state="visible" r:id="rId2"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
   <si>
     <t xml:space="preserve">Requirement ID</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">Story Points</t>
+    <t xml:space="preserve">story points </t>
   </si>
   <si>
     <t xml:space="preserve">Priority</t>
@@ -200,6 +200,9 @@
   </si>
   <si>
     <t xml:space="preserve">Add settings menu, for sound, graphics, fullscreen, etc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL:</t>
   </si>
 </sst>
 </file>
@@ -212,7 +215,7 @@
   <fonts count="5">
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
@@ -240,7 +243,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -249,8 +252,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2A6099"/>
-        <bgColor rgb="FF666699"/>
+        <fgColor rgb="FFFFA6A6"/>
+        <bgColor rgb="FFFFB66C"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFB66C"/>
+        <bgColor rgb="FFFFA6A6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE994"/>
+        <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFD095"/>
+        <bgColor rgb="FF99CCFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -288,7 +309,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -297,12 +318,40 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -330,7 +379,7 @@
       <rgbColor rgb="FF808000"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
+      <rgbColor rgb="FFAFD095"/>
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
@@ -338,7 +387,7 @@
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF2A6099"/>
+      <rgbColor rgb="FF0066CC"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -351,11 +400,11 @@
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFCCFFFF"/>
       <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
+      <rgbColor rgb="FFFFE994"/>
       <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
+      <rgbColor rgb="FFFFA6A6"/>
       <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
+      <rgbColor rgb="FFFFB66C"/>
       <rgbColor rgb="FF3366FF"/>
       <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FF99CC00"/>
@@ -377,185 +426,13 @@
 </styleSheet>
 </file>
 
-<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
-  <a:themeElements>
-    <a:clrScheme name="Office">
-      <a:dk1>
-        <a:srgbClr val="000000"/>
-      </a:dk1>
-      <a:lt1>
-        <a:srgbClr val="FFFFFF"/>
-      </a:lt1>
-      <a:dk2>
-        <a:srgbClr val="0E2841"/>
-      </a:dk2>
-      <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
-      </a:lt2>
-      <a:accent1>
-        <a:srgbClr val="156082"/>
-      </a:accent1>
-      <a:accent2>
-        <a:srgbClr val="E97132"/>
-      </a:accent2>
-      <a:accent3>
-        <a:srgbClr val="196B24"/>
-      </a:accent3>
-      <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
-      </a:accent4>
-      <a:accent5>
-        <a:srgbClr val="A02B93"/>
-      </a:accent5>
-      <a:accent6>
-        <a:srgbClr val="4EA72E"/>
-      </a:accent6>
-      <a:hlink>
-        <a:srgbClr val="467886"/>
-      </a:hlink>
-      <a:folHlink>
-        <a:srgbClr val="96607D"/>
-      </a:folHlink>
-    </a:clrScheme>
-    <a:fontScheme name="Office">
-      <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:majorFont>
-      <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204" pitchFamily="0" charset="1"/>
-        <a:ea typeface=""/>
-        <a:cs typeface=""/>
-      </a:minorFont>
-    </a:fontScheme>
-    <a:fmtScheme>
-      <a:fillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:fillStyleLst>
-      <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-      </a:lnStyleLst>
-      <a:effectStyleLst>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-      </a:effectStyleLst>
-      <a:bgFillStyleLst>
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:gradFill>
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="50000">
-              <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
-        </a:gradFill>
-      </a:bgFillStyleLst>
-    </a:fmtScheme>
-  </a:themeElements>
-</a:theme>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:K26"/>
-  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:K31"/>
+  <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.76"/>
@@ -565,7 +442,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="19.98"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" s="2" customFormat="true" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -575,7 +452,7 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -591,262 +468,285 @@
         <f aca="false">COUNTA(B2:B10000)</f>
         <v>25</v>
       </c>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" s="1" t="n">
+      <c r="D2" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="F2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="1" t="n">
+      <c r="I2" s="4" t="n">
         <f aca="false">SUM(D:D)</f>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="1" t="n">
+      <c r="D3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="F3" s="4"/>
+      <c r="H3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="1" t="n">
+      <c r="I3" s="4" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
+    <row r="4" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="1" t="n">
+      <c r="D4" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="F4" s="4"/>
+      <c r="H4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="1" t="n">
+      <c r="I4" s="4" t="n">
         <f aca="false">I2/I3</f>
-        <v>12.6666666666667</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+        <v>33.6666666666667</v>
+      </c>
+    </row>
+    <row r="5" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="1" t="n">
+      <c r="D5" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="E5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="4"/>
+      <c r="H5" s="4"/>
+    </row>
+    <row r="6" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="D6" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" s="4"/>
+      <c r="H6" s="4"/>
+    </row>
+    <row r="7" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="4" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="D7" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="4"/>
+      <c r="H7" s="4"/>
+    </row>
+    <row r="8" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="1" t="n">
+      <c r="D8" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4"/>
+      <c r="H8" s="4"/>
+    </row>
+    <row r="9" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="4"/>
+      <c r="H9" s="4"/>
+    </row>
+    <row r="10" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="4" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4"/>
+      <c r="H10" s="4"/>
+    </row>
+    <row r="11" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="4" t="n">
+        <v>9.2</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="1" t="n">
+      <c r="E11" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" s="4"/>
+      <c r="H11" s="4"/>
+    </row>
+    <row r="12" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4"/>
+      <c r="H12" s="4"/>
+    </row>
+    <row r="13" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D13" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4"/>
+      <c r="H13" s="4"/>
+    </row>
+    <row r="14" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="D14" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E9" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>9.2</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>5</v>
-      </c>
+      <c r="F14" s="4"/>
+      <c r="H14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="1" t="n">
-        <v>2</v>
+      <c r="D15" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E15" s="1" t="n">
         <v>5</v>
@@ -856,14 +756,14 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="1" t="n">
-        <v>2</v>
+      <c r="D16" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E16" s="1" t="n">
         <v>5</v>
@@ -873,14 +773,14 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="1" t="n">
-        <v>2</v>
+      <c r="D17" s="7" t="n">
+        <v>3</v>
       </c>
       <c r="E17" s="1" t="n">
         <v>5</v>
@@ -890,14 +790,14 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="1" t="n">
-        <v>8</v>
+      <c r="D18" s="8" t="n">
+        <v>13</v>
       </c>
       <c r="E18" s="1" t="n">
         <v>5</v>
@@ -907,116 +807,116 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D19" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="1" t="n">
+      <c r="D20" s="8" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="1" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="1" t="n">
-        <v>1</v>
+      <c r="D21" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="E21" s="1" t="n">
         <v>7</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="1" t="n">
-        <v>3</v>
+      <c r="D22" s="8" t="n">
+        <v>2</v>
       </c>
       <c r="E22" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="1" t="n">
-        <v>3</v>
+      <c r="D23" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="E23" s="1" t="n">
         <v>8</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="9" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="1" t="n">
-        <v>3</v>
+      <c r="D24" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
         <v>9</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="1" t="n">
-        <v>3</v>
+      <c r="D25" s="9" t="n">
+        <v>8</v>
       </c>
       <c r="E25" s="1" t="n">
         <v>9</v>
@@ -1026,19 +926,36 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="1" t="n">
-        <v>5</v>
+      <c r="D26" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="E26" s="1" t="n">
         <v>9</v>
       </c>
     </row>
+    <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C27" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D27" s="0" t="n">
+        <v>101</v>
+      </c>
+      <c r="E27" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="F27" s="10"/>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="D28" s="0"/>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/documentation/stack spreadsheet.xlsx
+++ b/documentation/stack spreadsheet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
   <si>
     <t xml:space="preserve">Requirement ID</t>
   </si>
@@ -203,6 +203,18 @@
   </si>
   <si>
     <t xml:space="preserve">TOTAL:</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 1: red </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 2: oragne </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 3: yellow </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sprint 4: green </t>
   </si>
 </sst>
 </file>
@@ -309,7 +321,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -326,15 +338,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -350,7 +354,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -466,286 +470,263 @@
       </c>
       <c r="I1" s="2" t="n">
         <f aca="false">COUNTA(B2:B10000)</f>
-        <v>25</v>
-      </c>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="2" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="n">
+        <v>29</v>
+      </c>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+    </row>
+    <row r="2" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E2" s="4" t="n">
+      <c r="D2" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="1" t="n">
         <f aca="false">SUM(D:D)</f>
         <v>202</v>
       </c>
     </row>
-    <row r="3" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
+    <row r="3" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E3" s="4" t="n">
+      <c r="D3" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="1" t="n">
         <v>6</v>
       </c>
     </row>
-    <row r="4" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
+    <row r="4" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="4" t="n">
+      <c r="D4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="1" t="n">
         <f aca="false">I2/I3</f>
         <v>33.6666666666667</v>
       </c>
     </row>
-    <row r="5" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="4" t="n">
+    <row r="5" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="4"/>
-      <c r="H5" s="4"/>
-    </row>
-    <row r="6" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="4" t="n">
+      <c r="E5" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" s="4"/>
-      <c r="H6" s="4"/>
-    </row>
-    <row r="7" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="n">
+      <c r="D6" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="4"/>
-      <c r="H7" s="4"/>
-    </row>
-    <row r="8" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="4" t="n">
+      <c r="D7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="E8" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F8" s="4"/>
-      <c r="H8" s="4"/>
-    </row>
-    <row r="9" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="4" t="n">
+      <c r="E8" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="4"/>
-      <c r="H9" s="4"/>
-    </row>
-    <row r="10" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="n">
+      <c r="D9" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>9.1</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F10" s="4"/>
-      <c r="H10" s="4"/>
-    </row>
-    <row r="11" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="n">
+      <c r="D10" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>9.2</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="7" t="n">
+      <c r="D11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="E11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F11" s="4"/>
-      <c r="H11" s="4"/>
-    </row>
-    <row r="12" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="4" t="n">
+      <c r="E11" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F12" s="4"/>
-      <c r="H12" s="4"/>
-    </row>
-    <row r="13" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="4" t="n">
+      <c r="D12" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C13" s="7" t="s">
+      <c r="C13" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="D13" s="7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="F13" s="4"/>
-      <c r="H13" s="4"/>
-    </row>
-    <row r="14" s="6" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="4" t="n">
+      <c r="D13" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C14" s="7" t="s">
+      <c r="C14" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="D14" s="7" t="n">
-        <v>3</v>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="D14" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="H14" s="4"/>
     </row>
     <row r="15" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="7" t="n">
+      <c r="D15" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="1" t="n">
@@ -756,13 +737,13 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="B16" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="7" t="n">
+      <c r="D16" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E16" s="1" t="n">
@@ -773,13 +754,13 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="B17" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="1" t="n">
@@ -790,13 +771,13 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="B18" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="C18" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="8" t="n">
+      <c r="D18" s="6" t="n">
         <v>13</v>
       </c>
       <c r="E18" s="1" t="n">
@@ -807,13 +788,13 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="B19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="C19" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="8" t="n">
+      <c r="D19" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="1" t="n">
@@ -824,13 +805,13 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="8" t="s">
+      <c r="B20" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="C20" s="8" t="s">
+      <c r="C20" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="D20" s="8" t="n">
+      <c r="D20" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="1" t="n">
@@ -841,13 +822,13 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="8" t="s">
+      <c r="B21" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="C21" s="8" t="s">
+      <c r="C21" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D21" s="8" t="n">
+      <c r="D21" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E21" s="1" t="n">
@@ -858,13 +839,13 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="8" t="s">
+      <c r="B22" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C22" s="8" t="s">
+      <c r="C22" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D22" s="8" t="n">
+      <c r="D22" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="1" t="n">
@@ -875,13 +856,13 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="9" t="s">
+      <c r="B23" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="C23" s="9" t="s">
+      <c r="C23" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="D23" s="9" t="n">
+      <c r="D23" s="7" t="n">
         <v>8</v>
       </c>
       <c r="E23" s="1" t="n">
@@ -892,13 +873,13 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="9" t="s">
+      <c r="B24" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="C24" s="9" t="s">
+      <c r="C24" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="D24" s="9" t="n">
+      <c r="D24" s="7" t="n">
         <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
@@ -909,13 +890,13 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="9" t="s">
+      <c r="B25" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C25" s="9" t="s">
+      <c r="C25" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="9" t="n">
+      <c r="D25" s="7" t="n">
         <v>8</v>
       </c>
       <c r="E25" s="1" t="n">
@@ -926,13 +907,13 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="9" t="s">
+      <c r="B26" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C26" s="9" t="s">
+      <c r="C26" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D26" s="9" t="n">
+      <c r="D26" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="1" t="n">
@@ -943,19 +924,34 @@
       <c r="C27" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D27" s="0" t="n">
+      <c r="D27" s="1" t="n">
         <v>101</v>
       </c>
       <c r="E27" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F27" s="10"/>
+      <c r="F27" s="8"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D28" s="0"/>
-    </row>
-    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B28" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/documentation/stack spreadsheet.xlsx
+++ b/documentation/stack spreadsheet.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Requirement ID</t>
   </si>
@@ -37,7 +37,7 @@
     <t xml:space="preserve">Priority</t>
   </si>
   <si>
-    <t xml:space="preserve">Sprint No.</t>
+    <t xml:space="preserve">assignemnt </t>
   </si>
   <si>
     <t xml:space="preserve">Total Items:</t>
@@ -49,6 +49,9 @@
     <t xml:space="preserve">Create a grid to store the tiles</t>
   </si>
   <si>
+    <t xml:space="preserve">ryan </t>
+  </si>
+  <si>
     <t xml:space="preserve">Total Story Points:</t>
   </si>
   <si>
@@ -58,6 +61,9 @@
     <t xml:space="preserve">Detect mouse movements to indicate swapping tiles</t>
   </si>
   <si>
+    <t xml:space="preserve">jett </t>
+  </si>
+  <si>
     <t xml:space="preserve">Sprints:</t>
   </si>
   <si>
@@ -67,6 +73,9 @@
     <t xml:space="preserve">Functionality to move/swap tiles</t>
   </si>
   <si>
+    <t xml:space="preserve">dani </t>
+  </si>
+  <si>
     <t xml:space="preserve">Story Points/Sprint:</t>
   </si>
   <si>
@@ -76,22 +85,34 @@
     <t xml:space="preserve">Detecting matches in a general sense (detecting every tile involved in tile in the match)</t>
   </si>
   <si>
+    <t xml:space="preserve">eliza </t>
+  </si>
+  <si>
     <t xml:space="preserve">Tile Clearing Mechanic</t>
   </si>
   <si>
     <t xml:space="preserve">Remove tiles after a match</t>
   </si>
   <si>
+    <t xml:space="preserve">emilia </t>
+  </si>
+  <si>
     <t xml:space="preserve">Tile Drop Mechanic</t>
   </si>
   <si>
     <t xml:space="preserve">Drop tiles when empty space exists</t>
   </si>
   <si>
+    <t xml:space="preserve">zach </t>
+  </si>
+  <si>
     <t xml:space="preserve">Create Tile Art Assets</t>
   </si>
   <si>
     <t xml:space="preserve">Create art assets for each of the tiles and powerups</t>
+  </si>
+  <si>
+    <t xml:space="preserve">adira </t>
   </si>
   <si>
     <t xml:space="preserve">Detecting Special Matches</t>
@@ -321,7 +342,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -331,6 +352,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -438,7 +463,7 @@
   <dimension ref="A1:K31"/>
   <sheetFormatPr defaultColWidth="8.59765625" defaultRowHeight="14.25" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="16.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="4.3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="32.76"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="86.65"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="1" width="11.55"/>
@@ -462,9 +487,10 @@
       <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="4" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="4"/>
       <c r="H1" s="2" t="s">
         <v>6</v>
       </c>
@@ -479,20 +505,23 @@
       <c r="A2" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E2" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F2" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="n">
         <f aca="false">SUM(D:D)</f>
@@ -503,20 +532,23 @@
       <c r="A3" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="C3" s="5" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="H3" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I3" s="1" t="n">
         <v>6</v>
@@ -526,20 +558,23 @@
       <c r="A4" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="4" t="n">
+      <c r="B4" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="5" t="n">
         <v>2</v>
       </c>
       <c r="E4" s="1" t="n">
         <v>1</v>
       </c>
+      <c r="F4" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="H4" s="1" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="I4" s="1" t="n">
         <f aca="false">I2/I3</f>
@@ -550,81 +585,93 @@
       <c r="A5" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="B5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>5</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="B6" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E6" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7" s="4" t="n">
+      <c r="B7" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="5" t="n">
         <v>3</v>
       </c>
       <c r="E7" s="1" t="n">
         <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="4" t="n">
+      <c r="B8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="5" t="n">
         <v>8</v>
       </c>
       <c r="E8" s="1" t="n">
         <v>3</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D9" s="5" t="n">
+      <c r="B9" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E9" s="1" t="n">
@@ -635,13 +682,13 @@
       <c r="A10" s="1" t="n">
         <v>9.1</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="5" t="n">
+      <c r="B10" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E10" s="1" t="n">
@@ -652,13 +699,13 @@
       <c r="A11" s="1" t="n">
         <v>9.2</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="5" t="n">
+      <c r="B11" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="6" t="n">
         <v>5</v>
       </c>
       <c r="E11" s="1" t="n">
@@ -669,13 +716,13 @@
       <c r="A12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" s="5" t="n">
+      <c r="B12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E12" s="1" t="n">
@@ -686,13 +733,13 @@
       <c r="A13" s="1" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="5" t="n">
+      <c r="B13" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D13" s="6" t="n">
         <v>2</v>
       </c>
       <c r="E13" s="1" t="n">
@@ -703,13 +750,13 @@
       <c r="A14" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="D14" s="5" t="n">
+      <c r="B14" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E14" s="1" t="n">
@@ -720,13 +767,13 @@
       <c r="A15" s="1" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="5" t="n">
+      <c r="B15" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E15" s="1" t="n">
@@ -737,13 +784,13 @@
       <c r="A16" s="1" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="D16" s="5" t="n">
+      <c r="B16" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E16" s="1" t="n">
@@ -754,13 +801,13 @@
       <c r="A17" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="D17" s="5" t="n">
+      <c r="B17" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="6" t="n">
         <v>3</v>
       </c>
       <c r="E17" s="1" t="n">
@@ -771,13 +818,13 @@
       <c r="A18" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="6" t="n">
+      <c r="B18" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="7" t="n">
         <v>13</v>
       </c>
       <c r="E18" s="1" t="n">
@@ -788,13 +835,13 @@
       <c r="A19" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" s="6" t="n">
+      <c r="B19" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E19" s="1" t="n">
@@ -805,13 +852,13 @@
       <c r="A20" s="1" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="6" t="n">
+      <c r="B20" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D20" s="7" t="n">
         <v>3</v>
       </c>
       <c r="E20" s="1" t="n">
@@ -822,13 +869,13 @@
       <c r="A21" s="1" t="n">
         <v>19</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="C21" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="6" t="n">
+      <c r="B21" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E21" s="1" t="n">
@@ -839,13 +886,13 @@
       <c r="A22" s="1" t="n">
         <v>20</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D22" s="6" t="n">
+      <c r="B22" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="7" t="n">
         <v>2</v>
       </c>
       <c r="E22" s="1" t="n">
@@ -856,13 +903,13 @@
       <c r="A23" s="1" t="n">
         <v>21</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>52</v>
-      </c>
-      <c r="C23" s="7" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="7" t="n">
+      <c r="B23" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E23" s="1" t="n">
@@ -873,13 +920,13 @@
       <c r="A24" s="1" t="n">
         <v>22</v>
       </c>
-      <c r="B24" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" s="7" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="7" t="n">
+      <c r="B24" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E24" s="1" t="n">
@@ -890,13 +937,13 @@
       <c r="A25" s="1" t="n">
         <v>23</v>
       </c>
-      <c r="B25" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="D25" s="7" t="n">
+      <c r="B25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D25" s="8" t="n">
         <v>8</v>
       </c>
       <c r="E25" s="1" t="n">
@@ -907,13 +954,13 @@
       <c r="A26" s="1" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D26" s="7" t="n">
+      <c r="B26" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="D26" s="8" t="n">
         <v>2</v>
       </c>
       <c r="E26" s="1" t="n">
@@ -922,7 +969,7 @@
     </row>
     <row r="27" customFormat="false" ht="15.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="D27" s="1" t="n">
         <v>101</v>
@@ -930,26 +977,26 @@
       <c r="E27" s="1" t="n">
         <v>115</v>
       </c>
-      <c r="F27" s="8"/>
+      <c r="F27" s="9"/>
     </row>
     <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
